--- a/data/trans_orig/PCS12_SP_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272014</t>
+          <t>271425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>320175</t>
+          <t>322551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>368559</t>
+          <t>369301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>420439</t>
+          <t>419918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>651276</t>
+          <t>654559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>726156</t>
+          <t>725744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373837</t>
+          <t>371461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>421998</t>
+          <t>422587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267912</t>
+          <t>268433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319792</t>
+          <t>319050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656207</t>
+          <t>656619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731087</t>
+          <t>727804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>350935</t>
+          <t>352567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>412347</t>
+          <t>415782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>554915</t>
+          <t>551349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>615301</t>
+          <t>613157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>921325</t>
+          <t>919994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1010021</t>
+          <t>1010277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549453</t>
+          <t>546018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>610865</t>
+          <t>609233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353092</t>
+          <t>355236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>413478</t>
+          <t>417044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920172</t>
+          <t>919916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1008868</t>
+          <t>1010199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>292792</t>
+          <t>290342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342563</t>
+          <t>343622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>364877</t>
+          <t>362846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>416722</t>
+          <t>415527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>670271</t>
+          <t>667935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>744809</t>
+          <t>739873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335946</t>
+          <t>334887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>385717</t>
+          <t>388167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>267119</t>
+          <t>268314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318964</t>
+          <t>320995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617541</t>
+          <t>622477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692079</t>
+          <t>694415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>371004</t>
+          <t>370172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>426945</t>
+          <t>427258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>527013</t>
+          <t>528927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>594121</t>
+          <t>594130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>914720</t>
+          <t>921725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1003645</t>
+          <t>1007201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>515277</t>
+          <t>514964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571218</t>
+          <t>572050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444491</t>
+          <t>444482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511599</t>
+          <t>509685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>977189</t>
+          <t>973633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1066114</t>
+          <t>1059109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1342788</t>
+          <t>1334686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1458215</t>
+          <t>1458948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1870650</t>
+          <t>1865497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1988583</t>
+          <t>1982855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3234788</t>
+          <t>3242413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3405160</t>
+          <t>3406066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1818328</t>
+          <t>1817595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1933755</t>
+          <t>1941857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1390614</t>
+          <t>1396342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1508547</t>
+          <t>1513700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3250581</t>
+          <t>3249675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3420953</t>
+          <t>3413328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290021</t>
+          <t>291826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>346088</t>
+          <t>345438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346334</t>
+          <t>343694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>397869</t>
+          <t>399080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>651593</t>
+          <t>652481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>730897</t>
+          <t>726191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357381</t>
+          <t>358031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413448</t>
+          <t>411643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299181</t>
+          <t>297970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350716</t>
+          <t>353356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>669622</t>
+          <t>674328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748926</t>
+          <t>748038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>415587</t>
+          <t>416935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>481524</t>
+          <t>480001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>539009</t>
+          <t>538650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605222</t>
+          <t>605340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>969750</t>
+          <t>969982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1064219</t>
+          <t>1060796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>536423</t>
+          <t>537946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>602360</t>
+          <t>601012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426962</t>
+          <t>426844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493175</t>
+          <t>493534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>985912</t>
+          <t>989335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1080381</t>
+          <t>1080149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>282089</t>
+          <t>280581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>337897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>380430</t>
+          <t>381069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>438748</t>
+          <t>438409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>676145</t>
+          <t>679672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>757730</t>
+          <t>759925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417728</t>
+          <t>419726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475534</t>
+          <t>477042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338426</t>
+          <t>338765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>396744</t>
+          <t>396105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>777067</t>
+          <t>774872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>858652</t>
+          <t>855125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>397007</t>
+          <t>398169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>460902</t>
+          <t>461560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>548258</t>
+          <t>546318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>612590</t>
+          <t>612409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>960741</t>
+          <t>961661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1054730</t>
+          <t>1054079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486837</t>
+          <t>486179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>550732</t>
+          <t>549570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439311</t>
+          <t>439492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503643</t>
+          <t>505583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>944910</t>
+          <t>945561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1038899</t>
+          <t>1037979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1445255</t>
+          <t>1454404</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1572564</t>
+          <t>1573064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1871924</t>
+          <t>1874277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2000271</t>
+          <t>1994639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3353430</t>
+          <t>3351809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3524304</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1854215</t>
+          <t>1853715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1981524</t>
+          <t>1972375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1558038</t>
+          <t>1563670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1686385</t>
+          <t>1684032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3460784</t>
+          <t>3459693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3631658</t>
+          <t>3633279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>318431</t>
+          <t>315169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>319101</t>
+          <t>318876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370863</t>
+          <t>370403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599455</t>
+          <t>601100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>674033</t>
+          <t>674318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356369</t>
+          <t>359631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301976</t>
+          <t>302436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353738</t>
+          <t>353963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673606</t>
+          <t>673321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748184</t>
+          <t>746539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345844</t>
+          <t>345939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>408778</t>
+          <t>404936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457884</t>
+          <t>458383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>523941</t>
+          <t>521511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>818496</t>
+          <t>819016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>912252</t>
+          <t>909925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>613653</t>
+          <t>617495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676587</t>
+          <t>676492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>518972</t>
+          <t>521402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>585029</t>
+          <t>584530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1153092</t>
+          <t>1155419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1246848</t>
+          <t>1246328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278881</t>
+          <t>277765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>335634</t>
+          <t>335397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>357585</t>
+          <t>355864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>412940</t>
+          <t>412866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652990</t>
+          <t>655432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>730656</t>
+          <t>733420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423918</t>
+          <t>424155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480671</t>
+          <t>481787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372071</t>
+          <t>372145</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>427426</t>
+          <t>429147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813907</t>
+          <t>811143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>891573</t>
+          <t>889131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316544</t>
+          <t>315738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>375050</t>
+          <t>375840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441266</t>
+          <t>443212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507162</t>
+          <t>509929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>780164</t>
+          <t>778602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>867857</t>
+          <t>864645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562517</t>
+          <t>561727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621023</t>
+          <t>621829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>536617</t>
+          <t>533850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602513</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1113489</t>
+          <t>1116701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1201182</t>
+          <t>1202744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1270293</t>
+          <t>1265887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1381491</t>
+          <t>1383208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1629512</t>
+          <t>1638475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1758713</t>
+          <t>1758059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2930007</t>
+          <t>2927561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3097352</t>
+          <t>3102177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2012859</t>
+          <t>2011142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2124057</t>
+          <t>2128463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1785829</t>
+          <t>1786483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1915030</t>
+          <t>1906067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3841540</t>
+          <t>3836715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4008885</t>
+          <t>4011331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289181</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347332</t>
+          <t>350289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>344521</t>
+          <t>343725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>385655</t>
+          <t>386736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>648223</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>717960</t>
+          <t>721432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282832</t>
+          <t>279875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340983</t>
+          <t>336473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284206</t>
+          <t>283125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325340</t>
+          <t>326136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582064</t>
+          <t>578592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>651801</t>
+          <t>651402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422403</t>
+          <t>431867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>869290</t>
+          <t>882277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>452491</t>
+          <t>454658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>507694</t>
+          <t>508104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>922145</t>
+          <t>926346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1405031</t>
+          <t>1438564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319022</t>
+          <t>306035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>765909</t>
+          <t>756445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445145</t>
+          <t>444735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500348</t>
+          <t>498181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736120</t>
+          <t>702587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1219006</t>
+          <t>1214805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284846</t>
+          <t>285413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342758</t>
+          <t>344891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>451342</t>
+          <t>450603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>739759</t>
+          <t>739663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>750391</t>
+          <t>755047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1145161</t>
+          <t>1159167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359568</t>
+          <t>357435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417480</t>
+          <t>416913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191872</t>
+          <t>191968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480289</t>
+          <t>481028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488795</t>
+          <t>474789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883565</t>
+          <t>878909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>450889</t>
+          <t>451739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>516546</t>
+          <t>518039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473485</t>
+          <t>463002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>630036</t>
+          <t>631214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>938718</t>
+          <t>936886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1128301</t>
+          <t>1124632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406363</t>
+          <t>404870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472020</t>
+          <t>471170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459237</t>
+          <t>458059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615788</t>
+          <t>626271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>883881</t>
+          <t>887550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1073464</t>
+          <t>1075296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1557120</t>
+          <t>1563703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2116180</t>
+          <t>2095632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1855580</t>
+          <t>1855890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2301535</t>
+          <t>2301980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3473685</t>
+          <t>3474211</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4140835</t>
+          <t>4180808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1327531</t>
+          <t>1348079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1886591</t>
+          <t>1880008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1342068</t>
+          <t>1341623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1788023</t>
+          <t>1787713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2946479</t>
+          <t>2906506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3613629</t>
+          <t>3613103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>271425</t>
+          <t>271561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>322551</t>
+          <t>323288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>369301</t>
+          <t>366634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>419918</t>
+          <t>421056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654559</t>
+          <t>654932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>725744</t>
+          <t>730336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371461</t>
+          <t>370724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422587</t>
+          <t>422451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268433</t>
+          <t>267295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319050</t>
+          <t>321717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>656619</t>
+          <t>652027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>727804</t>
+          <t>727431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>352567</t>
+          <t>348017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>415782</t>
+          <t>411343</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>551349</t>
+          <t>550050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>613157</t>
+          <t>611712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>919994</t>
+          <t>922126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1010277</t>
+          <t>1009392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>546018</t>
+          <t>550457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>609233</t>
+          <t>613783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355236</t>
+          <t>356681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417044</t>
+          <t>418343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919916</t>
+          <t>920801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010199</t>
+          <t>1008067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290342</t>
+          <t>291319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>343622</t>
+          <t>342150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>362846</t>
+          <t>363353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>415527</t>
+          <t>411789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667935</t>
+          <t>666670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>739873</t>
+          <t>741818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334887</t>
+          <t>336359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388167</t>
+          <t>387190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268314</t>
+          <t>272052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320995</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622477</t>
+          <t>620532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>694415</t>
+          <t>695680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>370172</t>
+          <t>372373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>427258</t>
+          <t>430526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>528927</t>
+          <t>529206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>594130</t>
+          <t>592843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>921725</t>
+          <t>913018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1007201</t>
+          <t>1000938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514964</t>
+          <t>511696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572050</t>
+          <t>569849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444482</t>
+          <t>445769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509685</t>
+          <t>509406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>973633</t>
+          <t>979896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1059109</t>
+          <t>1067816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1334686</t>
+          <t>1334087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1458948</t>
+          <t>1455877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1865497</t>
+          <t>1867507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1982855</t>
+          <t>1984856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3242413</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3406066</t>
+          <t>3411872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1820666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1941857</t>
+          <t>1942456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1396342</t>
+          <t>1394341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1513700</t>
+          <t>1511690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3249675</t>
+          <t>3243869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3413328</t>
+          <t>3413200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291826</t>
+          <t>291790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345438</t>
+          <t>344842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343694</t>
+          <t>346520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>399080</t>
+          <t>398662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>652481</t>
+          <t>653359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>726191</t>
+          <t>724680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358031</t>
+          <t>358627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411643</t>
+          <t>411679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297970</t>
+          <t>298388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353356</t>
+          <t>350530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674328</t>
+          <t>675839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748038</t>
+          <t>747160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>416935</t>
+          <t>416993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>480001</t>
+          <t>482445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>538650</t>
+          <t>539747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605340</t>
+          <t>604571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>969982</t>
+          <t>967673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1060796</t>
+          <t>1064915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>537946</t>
+          <t>535502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>601012</t>
+          <t>600954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426844</t>
+          <t>427613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493534</t>
+          <t>492437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>989335</t>
+          <t>985216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1080149</t>
+          <t>1082458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>280581</t>
+          <t>280512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337897</t>
+          <t>340049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381069</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>438409</t>
+          <t>438782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679672</t>
+          <t>677698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>759925</t>
+          <t>760294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419726</t>
+          <t>417574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477042</t>
+          <t>477111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338765</t>
+          <t>338392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>396105</t>
+          <t>398536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>774872</t>
+          <t>774503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>855125</t>
+          <t>857099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>398169</t>
+          <t>399286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>461560</t>
+          <t>463299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>546318</t>
+          <t>547740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>612409</t>
+          <t>613933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>961661</t>
+          <t>963719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1054079</t>
+          <t>1057283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486179</t>
+          <t>484440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549570</t>
+          <t>548453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439492</t>
+          <t>437968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>504161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945561</t>
+          <t>942357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1037979</t>
+          <t>1035921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1454404</t>
+          <t>1445018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1573064</t>
+          <t>1567650</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1874277</t>
+          <t>1876130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1994639</t>
+          <t>1990743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3351809</t>
+          <t>3363111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3526124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1853715</t>
+          <t>1859129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1972375</t>
+          <t>1981761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1563670</t>
+          <t>1567566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1684032</t>
+          <t>1682179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3459693</t>
+          <t>3458964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3633279</t>
+          <t>3621977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>265392</t>
+          <t>264685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>315169</t>
+          <t>317405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>318876</t>
+          <t>317285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370403</t>
+          <t>370077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601100</t>
+          <t>601826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>674318</t>
+          <t>674320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359631</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409408</t>
+          <t>410115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302436</t>
+          <t>302762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353963</t>
+          <t>355554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673321</t>
+          <t>673319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746539</t>
+          <t>745813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345939</t>
+          <t>346064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>404936</t>
+          <t>409876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>458383</t>
+          <t>454502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>521511</t>
+          <t>519751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819016</t>
+          <t>823455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>909925</t>
+          <t>914763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>617495</t>
+          <t>612555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676492</t>
+          <t>676367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521402</t>
+          <t>523162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>584530</t>
+          <t>588411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1155419</t>
+          <t>1150581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1246328</t>
+          <t>1241889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>277765</t>
+          <t>278753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>335397</t>
+          <t>337328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355864</t>
+          <t>355583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>412866</t>
+          <t>414009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>655432</t>
+          <t>653511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>733420</t>
+          <t>734039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424155</t>
+          <t>422224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481787</t>
+          <t>480799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372145</t>
+          <t>371002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429147</t>
+          <t>429428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811143</t>
+          <t>810524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>889131</t>
+          <t>891052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>315738</t>
+          <t>317739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>375840</t>
+          <t>377263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>443212</t>
+          <t>443368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509929</t>
+          <t>508293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>778602</t>
+          <t>777880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>864645</t>
+          <t>864870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561727</t>
+          <t>560304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621829</t>
+          <t>619828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>533850</t>
+          <t>535486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600567</t>
+          <t>600411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1116701</t>
+          <t>1116476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1202744</t>
+          <t>1203466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1265887</t>
+          <t>1270190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1383208</t>
+          <t>1384774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1638475</t>
+          <t>1632684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1758059</t>
+          <t>1752258</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2927561</t>
+          <t>2928023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3102177</t>
+          <t>3099135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2011142</t>
+          <t>2009576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2128463</t>
+          <t>2124160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1786483</t>
+          <t>1792284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1906067</t>
+          <t>1911858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3836715</t>
+          <t>3839757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4011331</t>
+          <t>4010869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>320510</t>
+          <t>346343</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293691</t>
+          <t>316867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350289</t>
+          <t>374752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>364395</t>
+          <t>389284</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343725</t>
+          <t>367499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>386736</t>
+          <t>411799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>684904</t>
+          <t>735627</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>648622</t>
+          <t>696721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>721432</t>
+          <t>768152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>309654</t>
+          <t>338428</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279875</t>
+          <t>310019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336473</t>
+          <t>367904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305466</t>
+          <t>337747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283125</t>
+          <t>315232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326136</t>
+          <t>359532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>615120</t>
+          <t>676175</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578592</t>
+          <t>643650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>651402</t>
+          <t>715081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>630164</t>
+          <t>684771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>669861</t>
+          <t>727031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1300024</t>
+          <t>1411802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>593664</t>
+          <t>384901</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>431867</t>
+          <t>351628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>882277</t>
+          <t>420143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>479906</t>
+          <t>531684</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>454658</t>
+          <t>502130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>508104</t>
+          <t>562040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1073570</t>
+          <t>916586</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>926346</t>
+          <t>872451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1438564</t>
+          <t>958388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>594648</t>
+          <t>658930</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306035</t>
+          <t>623688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>756445</t>
+          <t>692203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>472933</t>
+          <t>533427</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444735</t>
+          <t>503071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498181</t>
+          <t>562981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1067581</t>
+          <t>1192357</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702587</t>
+          <t>1150555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1214805</t>
+          <t>1236492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188312</t>
+          <t>1043831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952839</t>
+          <t>1065111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2141151</t>
+          <t>2108943</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>314566</t>
+          <t>362673</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285413</t>
+          <t>330994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344891</t>
+          <t>394367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>568177</t>
+          <t>420058</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>450603</t>
+          <t>395813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>739663</t>
+          <t>447987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>882743</t>
+          <t>782731</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>755047</t>
+          <t>741655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1159167</t>
+          <t>822860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>387760</t>
+          <t>437672</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>357435</t>
+          <t>405978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416913</t>
+          <t>469351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>363454</t>
+          <t>390345</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191968</t>
+          <t>362416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481028</t>
+          <t>414590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>751213</t>
+          <t>828018</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474789</t>
+          <t>787889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878909</t>
+          <t>869094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>800345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931631</t>
+          <t>810403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633956</t>
+          <t>1610749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>486171</t>
+          <t>504639</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451739</t>
+          <t>473434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518039</t>
+          <t>536326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>581314</t>
+          <t>625950</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>463002</t>
+          <t>596283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>631214</t>
+          <t>654925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1067485</t>
+          <t>1130589</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>936886</t>
+          <t>1087743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1124632</t>
+          <t>1178599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>436738</t>
+          <t>481516</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404870</t>
+          <t>449829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471170</t>
+          <t>512721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>507959</t>
+          <t>487132</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458059</t>
+          <t>458157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626271</t>
+          <t>516799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>944697</t>
+          <t>968648</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>887550</t>
+          <t>920638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1075296</t>
+          <t>1011494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>922909</t>
+          <t>986155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089273</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012182</t>
+          <t>2099237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1563703</t>
+          <t>1537537</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2095632</t>
+          <t>1660921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1855890</t>
+          <t>1917711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2301980</t>
+          <t>2026014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3474211</t>
+          <t>3480317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4180808</t>
+          <t>3649031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1728800</t>
+          <t>1916546</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1348079</t>
+          <t>1854182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1880008</t>
+          <t>1977566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1649811</t>
+          <t>1748651</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1341623</t>
+          <t>1689613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1787713</t>
+          <t>1797916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3378611</t>
+          <t>3665197</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2906506</t>
+          <t>3581699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3613103</t>
+          <t>3750413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
